--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B2" t="n">
-        <v>79423</v>
+        <v>80053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B3" t="n">
-        <v>80053</v>
+        <v>79423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B2" t="n">
-        <v>80053</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B3" t="n">
-        <v>79423</v>
+        <v>80079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>80084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B3" t="n">
-        <v>80079</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>79455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>80085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129600000</v>
       </c>
       <c r="B2" t="n">
-        <v>79455</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -779,7 +779,7 @@
         <v>129600011</v>
       </c>
       <c r="B3" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>80090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B3" t="n">
-        <v>80090</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B2" t="n">
-        <v>80090</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>80090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B2" t="n">
-        <v>80090</v>
+        <v>79463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>80093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 69571-2020 artfynd.xlsx
+++ b/artfynd/A 69571-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129600000</v>
+        <v>129600011</v>
       </c>
       <c r="B2" t="n">
-        <v>79463</v>
+        <v>80096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,39 +769,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129600011</v>
+        <v>129600000</v>
       </c>
       <c r="B3" t="n">
-        <v>80093</v>
+        <v>79466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
